--- a/new-stats/pohang-steelers.xlsx
+++ b/new-stats/pohang-steelers.xlsx
@@ -2185,22 +2185,58 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pohang</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Anyang</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>9</v>
+      </c>
+      <c r="N33" t="n">
+        <v>20</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>

--- a/new-stats/pohang-steelers.xlsx
+++ b/new-stats/pohang-steelers.xlsx
@@ -2239,22 +2239,58 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ulsan HD</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Pohang</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>8</v>
+      </c>
+      <c r="N34" t="n">
+        <v>18</v>
+      </c>
+      <c r="O34" t="n">
+        <v>5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
